--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$63</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,22 +452,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>RequestGroup.extension:Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t>Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/mii-ex-seltene-empfehlung-evidenzgraduierung}
-</t>
-  </si>
-  <si>
-    <t>MII EX SE Empfehlung Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t>Evidenzgraduierung der (einzelnen) Empfehlung</t>
   </si>
   <si>
     <t>RequestGroup.extension:Publikation</t>
@@ -1561,12 +1545,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL64"/>
+  <dimension ref="A1:AL63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.68359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2701,7 +2685,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>85</v>
@@ -2791,18 +2775,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2812,25 +2794,29 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>75</v>
       </c>
@@ -2878,7 +2864,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2887,7 +2873,7 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>133</v>
@@ -2899,16 +2885,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2918,28 +2904,26 @@
         <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -2988,7 +2972,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3000,21 +2984,21 @@
         <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3028,7 +3012,7 @@
         <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>75</v>
@@ -3037,18 +3021,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>161</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>75</v>
       </c>
@@ -3096,7 +3078,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3111,10 +3093,10 @@
         <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3145,13 +3127,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3217,7 +3199,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3225,14 +3207,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3248,19 +3230,21 @@
         <v>75</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
       </c>
@@ -3308,7 +3292,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3323,7 +3307,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3331,14 +3315,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3357,17 +3341,19 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>75</v>
@@ -3416,7 +3402,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3431,7 +3417,7 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3439,21 +3425,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -3462,22 +3448,22 @@
         <v>75</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3526,13 +3512,13 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>75</v>
@@ -3541,7 +3527,7 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3549,18 +3535,18 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>188</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
@@ -3569,26 +3555,24 @@
         <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O19" t="s" s="2">
         <v>192</v>
       </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
       </c>
@@ -3612,13 +3596,13 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3636,10 +3620,10 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>84</v>
@@ -3651,22 +3635,22 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>75</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3676,7 +3660,7 @@
         <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>85</v>
@@ -3688,15 +3672,15 @@
         <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3720,31 +3704,31 @@
         <v>75</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3759,35 +3743,35 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>85</v>
@@ -3796,66 +3780,66 @@
         <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="P21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>203</v>
-      </c>
       <c r="AG21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>84</v>
@@ -3867,18 +3851,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3901,66 +3885,66 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q22" t="s" s="2">
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3975,18 +3959,18 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4000,26 +3984,24 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4068,7 +4050,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4083,18 +4065,18 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4108,7 +4090,7 @@
         <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -4117,13 +4099,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4174,7 +4156,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4189,18 +4171,18 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4223,13 +4205,13 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4280,7 +4262,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4295,18 +4277,18 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4329,13 +4311,13 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4386,7 +4368,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4401,18 +4383,18 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4423,7 +4405,7 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4435,7 +4417,7 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>247</v>
@@ -4492,13 +4474,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
@@ -4541,10 +4523,10 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>253</v>
@@ -4616,15 +4598,15 @@
         <v>254</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4647,10 +4629,10 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>258</v>
@@ -4704,7 +4686,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4722,10 +4704,10 @@
         <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>255</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>260</v>
       </c>
@@ -4738,13 +4720,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
@@ -4822,16 +4804,16 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>265</v>
       </c>
@@ -4844,13 +4826,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -4916,19 +4898,19 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4946,14 +4928,14 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -4965,15 +4947,17 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5022,19 +5006,19 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -5045,14 +5029,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5065,10 +5049,10 @@
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>127</v>
@@ -5080,9 +5064,11 @@
         <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -5160,39 +5146,35 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -5240,19 +5222,19 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -5263,10 +5245,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5289,13 +5271,13 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5346,7 +5328,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5369,10 +5351,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5392,16 +5374,16 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5452,7 +5434,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5475,10 +5457,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5501,13 +5483,13 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5558,7 +5540,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5581,10 +5563,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5604,16 +5586,16 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>208</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5640,13 +5622,13 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -5664,7 +5646,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5679,7 +5661,7 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5687,10 +5669,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5701,7 +5683,7 @@
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -5713,13 +5695,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5746,13 +5728,13 @@
         <v>75</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -5770,13 +5752,13 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
@@ -5785,7 +5767,7 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5793,10 +5775,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5819,13 +5801,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5876,7 +5858,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5891,7 +5873,7 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -5925,15 +5907,17 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -5997,7 +5981,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6005,10 +5989,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6019,7 +6003,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6034,14 +6018,12 @@
         <v>266</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6090,19 +6072,19 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -6113,21 +6095,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6139,15 +6121,17 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6196,19 +6180,19 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -6219,14 +6203,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6239,10 +6223,10 @@
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>127</v>
@@ -6254,9 +6238,11 @@
         <v>277</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -6327,46 +6313,44 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6390,13 +6374,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>75</v>
+        <v>312</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6414,19 +6398,19 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6437,10 +6421,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6448,7 +6432,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>84</v>
@@ -6463,16 +6447,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>315</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6498,13 +6482,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>317</v>
+        <v>75</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6522,10 +6506,10 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>84</v>
@@ -6559,7 +6543,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -6571,17 +6555,15 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>323</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6636,7 +6618,7 @@
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>75</v>
@@ -6653,10 +6635,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6667,7 +6649,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -6682,10 +6664,10 @@
         <v>266</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>326</v>
+        <v>268</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6736,19 +6718,19 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>324</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6759,21 +6741,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6785,15 +6767,17 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N49" s="2"/>
+      <c r="N49" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6842,19 +6826,19 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6865,14 +6849,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6885,10 +6869,10 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>127</v>
@@ -6900,9 +6884,11 @@
         <v>277</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -6973,46 +6959,42 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -7060,19 +7042,19 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
@@ -7083,10 +7065,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7109,13 +7091,13 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7142,13 +7124,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>331</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>332</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7166,7 +7148,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
@@ -7200,7 +7182,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>84</v>
@@ -7215,13 +7197,13 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>334</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7248,13 +7230,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>336</v>
+        <v>75</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7275,7 +7257,7 @@
         <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>84</v>
@@ -7295,10 +7277,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7321,13 +7303,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7378,7 +7360,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7393,7 +7375,7 @@
         <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7415,7 +7397,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7490,7 +7472,7 @@
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
@@ -7502,15 +7484,15 @@
         <v>346</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7521,7 +7503,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7533,7 +7515,7 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>348</v>
+        <v>216</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>349</v>
@@ -7566,13 +7548,13 @@
         <v>75</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>75</v>
@@ -7590,13 +7572,13 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
@@ -7605,18 +7587,18 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>352</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7639,13 +7621,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7672,7 +7654,7 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>356</v>
+        <v>193</v>
       </c>
       <c r="Y57" t="s" s="2">
         <v>357</v>
@@ -7696,7 +7678,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7778,7 +7760,7 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>362</v>
@@ -7884,7 +7866,7 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>367</v>
@@ -7990,7 +7972,7 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>372</v>
@@ -8096,7 +8078,7 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Y61" t="s" s="2">
         <v>377</v>
@@ -8141,7 +8123,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>379</v>
       </c>
@@ -8154,13 +8136,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>75</v>
@@ -8169,15 +8151,17 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>380</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8202,13 +8186,13 @@
         <v>75</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>383</v>
+        <v>75</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>75</v>
@@ -8235,7 +8219,7 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>384</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>96</v>
@@ -8247,12 +8231,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8260,13 +8244,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>75</v>
@@ -8275,7 +8259,7 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>385</v>
+        <v>75</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>386</v>
@@ -8283,9 +8267,7 @@
       <c r="M63" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -8334,16 +8316,16 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>96</v>
@@ -8355,114 +8337,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AL64">
+  <autoFilter ref="A1:AL63">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8472,7 +8348,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
